--- a/resources/data-imports/Monsters/twisted-memories-delve-monsters.xlsx
+++ b/resources/data-imports/Monsters/twisted-memories-delve-monsters.xlsx
@@ -278,7 +278,7 @@
     <numFmt numFmtId="169" formatCode="0%"/>
     <numFmt numFmtId="170" formatCode="0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -320,11 +320,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -429,7 +424,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -463,34 +458,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -860,7 +855,7 @@
         <v>0.015955343603399</v>
       </c>
       <c r="W2" s="6" t="n">
-        <v>1008242009.45287</v>
+        <v>25000000</v>
       </c>
       <c r="X2" s="5" t="n">
         <v>0</v>
@@ -990,7 +985,7 @@
         <v>0.0201539066179668</v>
       </c>
       <c r="W3" s="4" t="n">
-        <v>1169005492.09072</v>
+        <v>29855502</v>
       </c>
       <c r="X3" s="5" t="n">
         <v>0</v>
@@ -1120,7 +1115,7 @@
         <v>0.0254572989502525</v>
       </c>
       <c r="W4" s="4" t="n">
-        <v>1355402599.50074</v>
+        <v>35654041</v>
       </c>
       <c r="X4" s="5" t="n">
         <v>0</v>
@@ -1250,7 +1245,7 @@
         <v>0.0321562505040478</v>
       </c>
       <c r="W5" s="4" t="n">
-        <v>1571520595.20931</v>
+        <v>42578772</v>
       </c>
       <c r="X5" s="5" t="n">
         <v>0</v>
@@ -1380,7 +1375,7 @@
         <v>0.0406179951965728</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>1822098454.05102</v>
+        <v>50848424</v>
       </c>
       <c r="X6" s="5" t="n">
         <v>0</v>
@@ -1510,7 +1505,7 @@
         <v>0.0513064025789055</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>2112630777.08054</v>
+        <v>60724210</v>
       </c>
       <c r="X7" s="5" t="n">
         <v>0</v>
@@ -1640,7 +1635,7 @@
         <v>0.0648074069842528</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>2449488275.64449</v>
+        <v>72518071</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>0</v>
@@ -1770,7 +1765,7 @@
         <v>0.0818611282200753</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>2840057466.55421</v>
+        <v>86602538</v>
       </c>
       <c r="X9" s="5" t="n">
         <v>0</v>
@@ -1900,7 +1895,7 @@
         <v>0.103402444647907</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>3292902641.55605</v>
+        <v>103422491</v>
       </c>
       <c r="X10" s="5" t="n">
         <v>0</v>
@@ -2030,7 +2025,7 @@
         <v>0.13061224285132</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>3817953662.72031</v>
+        <v>123509216</v>
       </c>
       <c r="X11" s="5" t="n">
         <v>0</v>
@@ -2160,7 +2155,7 @@
         <v>0.164982153378881</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>4426723701.6735</v>
+        <v>147497187</v>
       </c>
       <c r="X12" s="5" t="n">
         <v>0</v>
@@ -2290,7 +2285,7 @@
         <v>0.208396321350341</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>5132561697.19875</v>
+        <v>176144104</v>
       </c>
       <c r="X13" s="5" t="n">
         <v>0</v>
@@ -2420,7 +2415,7 @@
         <v>0.263234694558872</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>5950945067.0239</v>
+        <v>210354828</v>
       </c>
       <c r="X14" s="5" t="n">
         <v>0</v>
@@ -2550,7 +2545,7 @@
         <v>0.332503491282904</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>6899819092.29932</v>
+        <v>251209961</v>
       </c>
       <c r="X15" s="5" t="n">
         <v>0</v>
@@ -2680,7 +2675,7 @@
         <v>0.420000000002258</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>7999990416.69308</v>
+        <v>299999983</v>
       </c>
       <c r="X16" s="5" t="n">
         <v>0</v>
